--- a/figures_n_tables/tables/model-ablation.xlsx
+++ b/figures_n_tables/tables/model-ablation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoom618/Library/Mobile Documents/com~apple~CloudDocs/00-Paper/06-TSC/논문 작성/_figures and tables/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CD9CC1-C1CC-1A47-94F0-A83126185991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA64FDEC-BF54-B249-AFEB-A2ECE795CF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16660" windowHeight="18880" activeTab="1" xr2:uid="{BC76D622-9BC0-A344-B0B3-54E11F39A12E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="18980" xr2:uid="{BC76D622-9BC0-A344-B0B3-54E11F39A12E}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="152">
   <si>
     <t>✘</t>
   </si>
@@ -842,6 +864,16 @@
   </si>
   <si>
     <t>\quad only H2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>acc
+diff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rank
+diff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -995,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1106,6 +1138,9 @@
     </xf>
     <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1455,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE461C3E-B3FA-CA46-9891-0C6B5655930B}">
-  <dimension ref="A2:L30"/>
+  <dimension ref="A2:M30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1467,20 +1502,20 @@
     <col min="11" max="12" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="19">
+    <row r="2" spans="1:13" ht="19">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="37"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="10"/>
     </row>
-    <row r="3" spans="1:10" ht="19">
+    <row r="3" spans="1:13" ht="19">
       <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
@@ -1495,7 +1530,7 @@
       </c>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:10" ht="57">
+    <row r="4" spans="1:13" ht="57">
       <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
@@ -1523,8 +1558,14 @@
       <c r="J4" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="L4" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -1556,8 +1597,14 @@
       <c r="J5" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="L5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
@@ -1589,8 +1636,16 @@
       <c r="J6" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="L6" s="37">
+        <f>G6-G$5</f>
+        <v>0.4126673155706726</v>
+      </c>
+      <c r="M6" s="37">
+        <f>H6-H$5</f>
+        <v>0.1000000000000032</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
         <v>20</v>
       </c>
@@ -1622,8 +1677,16 @@
       <c r="J7" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="L7" s="37">
+        <f t="shared" ref="L7:M14" si="0">G7-G$5</f>
+        <v>-2.7270514530475509</v>
+      </c>
+      <c r="M7" s="37">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
@@ -1655,8 +1718,16 @@
       <c r="J8" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="L8" s="37">
+        <f t="shared" si="0"/>
+        <v>-0.63927649413695065</v>
+      </c>
+      <c r="M8" s="37">
+        <f t="shared" si="0"/>
+        <v>1.06666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -1688,8 +1759,16 @@
       <c r="J9" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="L9" s="37">
+        <f t="shared" si="0"/>
+        <v>-2.0800926631893049</v>
+      </c>
+      <c r="M9" s="37">
+        <f t="shared" si="0"/>
+        <v>2.4333333333333362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -1719,8 +1798,16 @@
       <c r="J10" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="L10" s="37">
+        <f t="shared" si="0"/>
+        <v>-1.1925944704341447</v>
+      </c>
+      <c r="M10" s="37">
+        <f t="shared" si="0"/>
+        <v>1.1666666666666701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1749,8 +1836,16 @@
       <c r="J11" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="L11" s="37">
+        <f t="shared" si="0"/>
+        <v>-1.2670420650618581</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" si="0"/>
+        <v>1.4666666666666699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1779,8 +1874,16 @@
       <c r="J12" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="L12" s="37">
+        <f t="shared" si="0"/>
+        <v>-2.9540512217906354</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="0"/>
+        <v>2.4333333333333398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
         <v>149</v>
       </c>
@@ -1813,8 +1916,13 @@
       <c r="J13" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="L13" s="37">
+        <f t="shared" si="0"/>
+        <v>-1.8672150399574292</v>
+      </c>
+      <c r="M13" s="37"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
         <v>1</v>
       </c>
@@ -1846,15 +1954,20 @@
       <c r="J14" s="2">
         <v>5</v>
       </c>
+      <c r="L14" s="37">
+        <f t="shared" si="0"/>
+        <v>-5.5595475902817242</v>
+      </c>
+      <c r="M14" s="37"/>
     </row>
     <row r="18" spans="1:10" ht="19">
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="37"/>
+      <c r="D18" s="38"/>
       <c r="E18" s="10" t="s">
         <v>30</v>
       </c>
@@ -2206,7 +2319,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A8F7CBD-6963-5041-8A74-6D577B03DFFA}">
-  <dimension ref="A2:AC48"/>
+  <dimension ref="A2:AC82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
@@ -2216,37 +2329,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:29">
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37" t="s">
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="37" t="s">
+      <c r="S2" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37" t="s">
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="1" t="s">
@@ -2262,12 +2375,12 @@
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="15" t="s">
         <v>50</v>
       </c>
@@ -2290,12 +2403,12 @@
       <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="37" t="s">
+      <c r="V3" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
       <c r="Z3" s="15" t="s">
         <v>50</v>
       </c>
@@ -3234,8 +3347,8 @@
       <c r="I16" s="24">
         <v>78.536585365853668</v>
       </c>
-      <c r="J16" s="24">
-        <v>80</v>
+      <c r="J16" s="25">
+        <v>80.487804878048792</v>
       </c>
       <c r="K16" s="24">
         <v>77.073170731707322</v>
@@ -5212,28 +5325,36 @@
         <v>92</v>
       </c>
       <c r="C43" s="24">
+        <f t="shared" ref="C43:I43" si="0">AVERAGE(C13:C22)</f>
         <v>77.412559417921017</v>
       </c>
       <c r="D43" s="24">
+        <f t="shared" si="0"/>
         <v>75.659250984996362</v>
       </c>
       <c r="E43" s="25">
+        <f t="shared" si="0"/>
         <v>77.714771444532929</v>
       </c>
       <c r="F43" s="24">
+        <f t="shared" si="0"/>
         <v>76.437546845610001</v>
       </c>
       <c r="G43" s="24">
+        <f t="shared" si="0"/>
         <v>76.899752380995693</v>
       </c>
       <c r="H43" s="24">
+        <f t="shared" si="0"/>
         <v>76.448495102012103</v>
       </c>
       <c r="I43" s="24">
+        <f t="shared" si="0"/>
         <v>75.855659988176029</v>
       </c>
       <c r="J43" s="26">
-        <v>78.778660895649992</v>
+        <f>AVERAGE(J13:J22)</f>
+        <v>78.827441383454868</v>
       </c>
       <c r="K43" s="24">
         <v>73.285704982668818</v>
@@ -5286,28 +5407,36 @@
         <v>93</v>
       </c>
       <c r="C44" s="26">
+        <f t="shared" ref="C44:I44" si="1">AVERAGE(C13:C42)</f>
         <v>80.214932277513725</v>
       </c>
       <c r="D44" s="24">
+        <f t="shared" si="1"/>
         <v>77.075213508895501</v>
       </c>
       <c r="E44" s="24">
+        <f t="shared" si="1"/>
         <v>79.162988467806102</v>
       </c>
       <c r="F44" s="24">
+        <f t="shared" si="1"/>
         <v>77.722172298753748</v>
       </c>
       <c r="G44" s="24">
+        <f t="shared" si="1"/>
         <v>78.609670491508908</v>
       </c>
       <c r="H44" s="24">
+        <f t="shared" si="1"/>
         <v>78.535222896881194</v>
       </c>
       <c r="I44" s="24">
+        <f t="shared" si="1"/>
         <v>76.848213740152417</v>
       </c>
       <c r="J44" s="25">
-        <v>79.802264961943052</v>
+        <f>AVERAGE(J13:J42)</f>
+        <v>79.818525124544678</v>
       </c>
       <c r="K44" s="24">
         <v>74.242717371661328</v>
@@ -5360,28 +5489,36 @@
         <v>94</v>
       </c>
       <c r="C45" s="28">
+        <f t="shared" ref="C45:I45" si="2">C80</f>
         <v>2.5333333333333332</v>
       </c>
       <c r="D45" s="27">
+        <f t="shared" si="2"/>
         <v>5.9333333333333336</v>
       </c>
       <c r="E45" s="27">
-        <v>3.5</v>
+        <f t="shared" si="2"/>
+        <v>3.5333333333333332</v>
       </c>
       <c r="F45" s="27">
+        <f t="shared" si="2"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G45" s="27">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="H45" s="27">
+        <f t="shared" si="2"/>
+        <v>3.9</v>
+      </c>
+      <c r="I45" s="27">
+        <f t="shared" si="2"/>
         <v>4.8666666666666663</v>
       </c>
-      <c r="G45" s="27">
-        <v>3.6</v>
-      </c>
-      <c r="H45" s="27">
-        <v>3.9</v>
-      </c>
-      <c r="I45" s="27">
-        <v>4.8666666666666663</v>
-      </c>
       <c r="J45" s="29">
-        <v>2.4333333333333331</v>
+        <f>J80</f>
+        <v>2.4</v>
       </c>
       <c r="K45" s="27" t="s">
         <v>41</v>
@@ -5433,37 +5570,47 @@
       <c r="B46" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="2" cm="1">
+        <f t="array" ref="C46">SUM(--($J13:$J42&gt;=C13:C42))</f>
         <v>25</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="2" cm="1">
+        <f t="array" ref="D46">SUM(--($J13:$J42&gt;=D13:D42))</f>
         <v>30</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="2" cm="1">
+        <f t="array" ref="E46">SUM(--($J13:$J42&gt;=E13:E42))</f>
         <v>22</v>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="2" cm="1">
+        <f t="array" ref="F46">SUM(--($J13:$J42&gt;=F13:F42))</f>
         <v>24</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="2" cm="1">
+        <f t="array" ref="G46">SUM(--($J13:$J42&gt;=G13:G42))</f>
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" cm="1">
+        <f t="array" ref="H46">SUM(--($J13:$J42&gt;=H13:H42))</f>
         <v>22</v>
       </c>
-      <c r="H46" s="30">
-        <v>22</v>
-      </c>
-      <c r="I46" s="30">
+      <c r="I46" s="2" cm="1">
+        <f t="array" ref="I46">SUM(--($J13:$J42&gt;=I13:I42))</f>
         <v>25</v>
       </c>
-      <c r="J46" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="K46" s="30">
+      <c r="J46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K46" s="2" cm="1">
+        <f t="array" ref="K46">SUM(--($J13:$J42&gt;=K13:K42))</f>
         <v>26</v>
       </c>
-      <c r="L46" s="30">
+      <c r="L46" s="2" cm="1">
+        <f t="array" ref="L46">SUM(--($J13:$J42&gt;=L13:L42))</f>
         <v>20</v>
       </c>
-      <c r="M46" s="30">
+      <c r="M46" s="2" cm="1">
+        <f t="array" ref="M46">SUM(--($J13:$J42&gt;=M13:M42))</f>
         <v>20</v>
       </c>
       <c r="R46" s="18" t="s">
@@ -5507,37 +5654,47 @@
       <c r="B47" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="2" cm="1">
+        <f t="array" ref="C47">SUM(--($J13:$J42&lt;=C13:C42))</f>
         <v>22</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="2" cm="1">
+        <f t="array" ref="D47">SUM(--($J13:$J42&lt;=D13:D42))</f>
         <v>5</v>
       </c>
-      <c r="E47" s="30">
-        <v>14</v>
-      </c>
-      <c r="F47" s="30">
-        <v>10</v>
-      </c>
-      <c r="G47" s="30">
+      <c r="E47" s="2" cm="1">
+        <f t="array" ref="E47">SUM(--($J13:$J42&lt;=E13:E42))</f>
+        <v>13</v>
+      </c>
+      <c r="F47" s="2" cm="1">
+        <f t="array" ref="F47">SUM(--($J13:$J42&lt;=F13:F42))</f>
+        <v>9</v>
+      </c>
+      <c r="G47" s="2" cm="1">
+        <f t="array" ref="G47">SUM(--($J13:$J42&lt;=G13:G42))</f>
         <v>15</v>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="2" cm="1">
+        <f t="array" ref="H47">SUM(--($J13:$J42&lt;=H13:H42))</f>
         <v>12</v>
       </c>
-      <c r="I47" s="30">
+      <c r="I47" s="2" cm="1">
+        <f t="array" ref="I47">SUM(--($J13:$J42&lt;=I13:I42))</f>
         <v>9</v>
       </c>
-      <c r="J47" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="K47" s="30">
+      <c r="J47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K47" s="2" cm="1">
+        <f t="array" ref="K47">SUM(--($J13:$J42&lt;=K13:K42))</f>
         <v>5</v>
       </c>
-      <c r="L47" s="30">
+      <c r="L47" s="2" cm="1">
+        <f t="array" ref="L47">SUM(--($J13:$J42&lt;=L13:L42))</f>
         <v>13</v>
       </c>
-      <c r="M47" s="30">
+      <c r="M47" s="2" cm="1">
+        <f t="array" ref="M47">SUM(--($J13:$J42&lt;=M13:M42))</f>
         <v>17</v>
       </c>
       <c r="R47" s="18" t="s">
@@ -5590,6 +5747,1080 @@
       <c r="L48" s="19"/>
       <c r="M48" s="19"/>
     </row>
+    <row r="50" spans="3:10">
+      <c r="C50" s="2">
+        <f>RANK(C13,$C13:$J13)</f>
+        <v>5</v>
+      </c>
+      <c r="D50" s="2">
+        <f t="shared" ref="D50:J50" si="3">RANK(D13,$C13:$J13)</f>
+        <v>8</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F50" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G50" s="2">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I50" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="J50" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10">
+      <c r="C51" s="2">
+        <f t="shared" ref="C51:J79" si="4">RANK(C14,$C14:$J14)</f>
+        <v>3</v>
+      </c>
+      <c r="D51" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F51" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="G51" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="I51" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10">
+      <c r="C52" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G52" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="I52" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10">
+      <c r="C53" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E53" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F53" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G53" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I53" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J53" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10">
+      <c r="C54" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E54" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F54" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="G54" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10">
+      <c r="C55" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D55" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F55" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G55" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="I55" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10">
+      <c r="C56" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G56" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="I56" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J56" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10">
+      <c r="C57" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="G57" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I57" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J57" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10">
+      <c r="C58" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E58" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F58" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I58" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J58" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10">
+      <c r="C59" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="I59" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J59" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10">
+      <c r="C60" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J60" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10">
+      <c r="C61" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I61" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J61" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10">
+      <c r="C62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10">
+      <c r="C63" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="I63" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J63" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10">
+      <c r="C64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10">
+      <c r="C65" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I65" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10">
+      <c r="C66" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E66" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="F66" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G66" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I66" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J66" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="3:10">
+      <c r="C67" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D67" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E67" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="F67" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G67" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J67" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="3:10">
+      <c r="C68" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D68" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="E68" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F68" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G68" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J68" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10">
+      <c r="C69" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E69" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="F69" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="G69" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H69" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J69" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10">
+      <c r="C70" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E70" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F70" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="G70" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H70" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J70" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10">
+      <c r="C71" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D71" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E71" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F71" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G71" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H71" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J71" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="3:10">
+      <c r="C72" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D72" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F72" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G72" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J72" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="3:10">
+      <c r="C73" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D73" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E73" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F73" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G73" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J73" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10">
+      <c r="C74" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="D74" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E74" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G74" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="I74" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J74" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="3:10">
+      <c r="C75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="E75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F75" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="G75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10">
+      <c r="C76" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D76" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E76" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="F76" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="G76" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H76" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="I76" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J76" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="3:10">
+      <c r="C77" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="D77" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="E77" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F77" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G77" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H77" s="2">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="I77" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J77" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="3:10">
+      <c r="C78" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D78" s="2">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="E78" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="F78" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G78" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H78" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I78" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J78" s="2">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10">
+      <c r="C79" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="E79" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="F79" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="G79" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H79" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="I79" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J79" s="2">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10">
+      <c r="C80" s="3">
+        <f>AVERAGE(C49:C79)</f>
+        <v>2.5333333333333332</v>
+      </c>
+      <c r="D80" s="3">
+        <f t="shared" ref="D80" si="5">AVERAGE(D49:D79)</f>
+        <v>5.9333333333333336</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" ref="E80" si="6">AVERAGE(E49:E79)</f>
+        <v>3.5333333333333332</v>
+      </c>
+      <c r="F80" s="3">
+        <f t="shared" ref="F80" si="7">AVERAGE(F49:F79)</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" ref="G80" si="8">AVERAGE(G49:G79)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H80" s="3">
+        <f t="shared" ref="H80" si="9">AVERAGE(H49:H79)</f>
+        <v>3.9</v>
+      </c>
+      <c r="I80" s="3">
+        <f t="shared" ref="I80" si="10">AVERAGE(I49:I79)</f>
+        <v>4.8666666666666663</v>
+      </c>
+      <c r="J80" s="3">
+        <f t="shared" ref="J80" si="11">AVERAGE(J49:J79)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="3:10">
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="V3:Y3"/>
@@ -5601,7 +6832,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B45">
-    <cfRule type="colorScale" priority="139">
+    <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5611,7 +6842,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:J13">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5621,7 +6852,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:J14">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5631,6 +6862,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:J15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:J16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5640,18 +6881,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:J16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C17:J17">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5661,7 +6892,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:J18">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5671,7 +6902,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:J19">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5681,7 +6912,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:J20">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5691,7 +6922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:J21">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5701,7 +6932,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:J22">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5711,7 +6942,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:J23">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5721,7 +6952,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:J24">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5731,7 +6962,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:J25">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5741,7 +6972,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:J26">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5751,7 +6982,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:J27">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5761,7 +6992,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:J28">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5771,7 +7002,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:J29">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5781,7 +7012,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:J30">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5791,7 +7022,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:J31">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5801,7 +7032,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:J32">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5811,7 +7042,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:J33">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5821,7 +7052,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34:J34">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5831,7 +7062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:J35">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5841,7 +7072,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:J36">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5851,7 +7082,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:J37">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5861,7 +7092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38:J38">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5871,7 +7102,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:J39">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5881,7 +7112,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:J40">
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5891,7 +7122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41:J41">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5901,7 +7132,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42:J42">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5911,7 +7142,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:J43">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5921,7 +7152,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:J44">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5931,7 +7162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45:J45">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5940,8 +7171,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C50:J79 C81:J81">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C48:M48">
-    <cfRule type="colorScale" priority="269">
+    <cfRule type="colorScale" priority="270">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5951,7 +7194,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R45">
-    <cfRule type="colorScale" priority="100">
+    <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
